--- a/03_Outputs/Rio_Grande/07_Ambiental/ambiental.xlsx
+++ b/03_Outputs/Rio_Grande/07_Ambiental/ambiental.xlsx
@@ -61,7 +61,7 @@
     <numFmt numFmtId="195" formatCode="0.0%"/>
     <numFmt numFmtId="196" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,23 +71,213 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -107,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -116,34 +306,68 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="16" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="18" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="22" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,14 +696,14 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="75.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,23 +1018,22 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="59" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="59" t="inlineStr">
         <is>
           <t>Antioquia</t>
         </is>
@@ -1026,17 +1249,17 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="61" t="inlineStr">
         <is>
           <t>perdida_ca</t>
         </is>
@@ -1104,17 +1327,17 @@
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="63" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
@@ -1272,17 +1495,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1348,22 +1571,23 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>imrc_deficit</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>imrc_exceso</t>
         </is>
@@ -1446,23 +1670,23 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="69" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="69" t="inlineStr">
         <is>
           <t>Pérdida de cobertura arbórea 2001-2023 (%)</t>
         </is>
@@ -1545,71 +1769,71 @@
   <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>IRCA</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Nivel de riesgo</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>IRCA urbano</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Nivel riesgo urbano</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>IRCA rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Nivel riesgo rural</t>
         </is>
@@ -1637,7 +1861,7 @@
       <c r="E2">
         <v>2007</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="11">
         <v>21</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -1645,7 +1869,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="13">
         <v>21</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -1653,7 +1877,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1686,7 +1910,7 @@
       <c r="E3">
         <v>2007</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="11">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -1694,7 +1918,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="13">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -1702,7 +1926,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J3" s="12" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1735,7 +1959,7 @@
       <c r="E4">
         <v>2007</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="11">
         <v>1.7</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -1743,7 +1967,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="13">
         <v>1.7</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -1751,7 +1975,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1784,7 +2008,7 @@
       <c r="E5">
         <v>2007</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="11">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -1792,7 +2016,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="13">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -1800,7 +2024,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1833,7 +2057,7 @@
       <c r="E6">
         <v>2007</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="11">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -1841,7 +2065,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="13">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -1849,7 +2073,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1861,49 +2085,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="3">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="10">
         <v>2007</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="12">
         <v>4.54</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H7" s="11">
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H7" s="14">
         <v>4.54</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J7" s="13" t="e">
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1931,7 +2155,7 @@
       <c r="E8">
         <v>2008</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="11">
         <v>3.7</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -1939,7 +2163,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="13">
         <v>3.7</v>
       </c>
       <c r="I8" t="inlineStr">
@@ -1947,7 +2171,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1980,7 +2204,7 @@
       <c r="E9">
         <v>2008</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="11">
         <v>0.5</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -1988,7 +2212,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="13">
         <v>0.5</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -1996,7 +2220,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2029,7 +2253,7 @@
       <c r="E10">
         <v>2008</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="11">
         <v>4.3</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -2037,7 +2261,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="13">
         <v>4.3</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -2045,7 +2269,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2078,7 +2302,7 @@
       <c r="E11">
         <v>2008</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="11">
         <v>2.8</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -2086,7 +2310,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="13">
         <v>2.8</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -2094,7 +2318,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2127,7 +2351,7 @@
       <c r="E12">
         <v>2008</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="11">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -2135,7 +2359,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="13">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
@@ -2143,7 +2367,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2155,49 +2379,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="3">
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="10">
         <v>2008</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="12">
         <v>2.26</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H13" s="11">
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H13" s="14">
         <v>2.26</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J13" s="13" t="e">
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2225,7 +2449,7 @@
       <c r="E14">
         <v>2009</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="11">
         <v>19.5</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -2233,7 +2457,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="13">
         <v>19.5</v>
       </c>
       <c r="I14" t="inlineStr">
@@ -2241,7 +2465,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J14" s="12" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2274,7 +2498,7 @@
       <c r="E15">
         <v>2009</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="11">
         <v>1.2</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -2282,7 +2506,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="13">
         <v>1.2</v>
       </c>
       <c r="I15" t="inlineStr">
@@ -2290,7 +2514,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2323,7 +2547,7 @@
       <c r="E16">
         <v>2009</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="11">
         <v>2.7</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -2331,7 +2555,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="13">
         <v>2.7</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -2339,7 +2563,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2372,7 +2596,7 @@
       <c r="E17">
         <v>2009</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="11">
         <v>0.9</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -2380,7 +2604,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="13">
         <v>0.9</v>
       </c>
       <c r="I17" t="inlineStr">
@@ -2388,7 +2612,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2421,7 +2645,7 @@
       <c r="E18">
         <v>2009</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="11">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -2429,7 +2653,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="13">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -2437,7 +2661,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2449,49 +2673,49 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E19" s="3">
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" s="10">
         <v>2009</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="12">
         <v>4.86</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H19" s="11">
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H19" s="14">
         <v>4.86</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J19" s="13" t="e">
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2519,7 +2743,7 @@
       <c r="E20">
         <v>2010</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="11">
         <v>59.2</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -2527,7 +2751,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="13">
         <v>29.4</v>
       </c>
       <c r="I20" t="inlineStr">
@@ -2535,7 +2759,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="15">
         <v>83.8</v>
       </c>
       <c r="K20" t="inlineStr">
@@ -2566,7 +2790,7 @@
       <c r="E21">
         <v>2010</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="11">
         <v>2.9</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -2574,7 +2798,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="13">
         <v>2.9</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -2582,7 +2806,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2615,7 +2839,7 @@
       <c r="E22">
         <v>2010</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="11">
         <v>4.6</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -2623,7 +2847,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="13">
         <v>0.7</v>
       </c>
       <c r="I22" t="inlineStr">
@@ -2631,7 +2855,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="15">
         <v>7.9</v>
       </c>
       <c r="K22" t="inlineStr">
@@ -2662,7 +2886,7 @@
       <c r="E23">
         <v>2010</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="11">
         <v>0.2</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -2670,7 +2894,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="13">
         <v>0.2</v>
       </c>
       <c r="I23" t="inlineStr">
@@ -2678,7 +2902,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2711,7 +2935,7 @@
       <c r="E24">
         <v>2010</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="11">
         <v>49.5</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -2719,7 +2943,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="13">
         <v>6.1</v>
       </c>
       <c r="I24" t="inlineStr">
@@ -2727,7 +2951,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="15">
         <v>72</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -2737,49 +2961,49 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E25" s="3">
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E25" s="10">
         <v>2010</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="12">
         <v>23.28</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H25" s="11">
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H25" s="14">
         <v>7.86</v>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J25" s="13">
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J25" s="16">
         <v>54.5666666666667</v>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2807,7 +3031,7 @@
       <c r="E26">
         <v>2011</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="11">
         <v>57</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -2815,7 +3039,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="13">
         <v>21.6</v>
       </c>
       <c r="I26" t="inlineStr">
@@ -2823,7 +3047,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="15">
         <v>89.2</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -2854,7 +3078,7 @@
       <c r="E27">
         <v>2011</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="11">
         <v>0.2</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -2862,7 +3086,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="13">
         <v>0.2</v>
       </c>
       <c r="I27" t="inlineStr">
@@ -2870,7 +3094,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="J27" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2903,7 +3127,7 @@
       <c r="E28">
         <v>2011</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="11">
         <v>2.5</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -2911,7 +3135,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="13">
         <v>0.4</v>
       </c>
       <c r="I28" t="inlineStr">
@@ -2919,7 +3143,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="15">
         <v>4.4</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -2950,7 +3174,7 @@
       <c r="E29">
         <v>2011</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="11">
         <v>0.9</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -2958,7 +3182,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="13">
         <v>0.9</v>
       </c>
       <c r="I29" t="inlineStr">
@@ -2966,7 +3190,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J29" s="12" t="inlineStr">
+      <c r="J29" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -2999,7 +3223,7 @@
       <c r="E30">
         <v>2011</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="11">
         <v>38.6</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -3007,7 +3231,7 @@
           <t>Riesgo alto</t>
         </is>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="13">
         <v>14.4</v>
       </c>
       <c r="I30" t="inlineStr">
@@ -3015,7 +3239,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="15">
         <v>62.2</v>
       </c>
       <c r="K30" t="inlineStr">
@@ -3025,49 +3249,49 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E31" s="3">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E31" s="10">
         <v>2011</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="12">
         <v>19.84</v>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H31" s="11">
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H31" s="14">
         <v>7.5</v>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J31" s="13">
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J31" s="16">
         <v>51.9333333333333</v>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3095,7 +3319,7 @@
       <c r="E32">
         <v>2012</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="11">
         <v>10.7</v>
       </c>
       <c r="G32" t="inlineStr">
@@ -3103,7 +3327,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="13">
         <v>10.7</v>
       </c>
       <c r="I32" t="inlineStr">
@@ -3111,7 +3335,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J32" s="12" t="inlineStr">
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3144,7 +3368,7 @@
       <c r="E33">
         <v>2012</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="11">
         <v>9.1</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -3152,7 +3376,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="13">
         <v>9.1</v>
       </c>
       <c r="I33" t="inlineStr">
@@ -3160,7 +3384,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J33" s="12" t="inlineStr">
+      <c r="J33" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3193,7 +3417,7 @@
       <c r="E34">
         <v>2012</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="11">
         <v>10.8</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -3201,7 +3425,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="13">
         <v>10.8</v>
       </c>
       <c r="I34" t="inlineStr">
@@ -3209,7 +3433,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J34" s="12" t="inlineStr">
+      <c r="J34" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3242,7 +3466,7 @@
       <c r="E35">
         <v>2012</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="11">
         <v>2.3</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -3250,7 +3474,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="13">
         <v>2.3</v>
       </c>
       <c r="I35" t="inlineStr">
@@ -3258,7 +3482,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="J35" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3291,7 +3515,7 @@
       <c r="E36">
         <v>2012</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="11">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -3299,7 +3523,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="13">
         <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
@@ -3307,7 +3531,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J36" s="12" t="inlineStr">
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3319,49 +3543,49 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E37" s="3">
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E37" s="10">
         <v>2012</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="12">
         <v>6.58</v>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H37" s="11">
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H37" s="14">
         <v>6.58</v>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J37" s="13" t="e">
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J37" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3389,7 +3613,7 @@
       <c r="E38">
         <v>2013</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="11">
         <v>7.1</v>
       </c>
       <c r="G38" t="inlineStr">
@@ -3397,7 +3621,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="13">
         <v>7.1</v>
       </c>
       <c r="I38" t="inlineStr">
@@ -3405,7 +3629,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3438,7 +3662,7 @@
       <c r="E39">
         <v>2013</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="11">
         <v>4.7</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -3446,7 +3670,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="13">
         <v>4.7</v>
       </c>
       <c r="I39" t="inlineStr">
@@ -3454,7 +3678,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J39" s="12" t="inlineStr">
+      <c r="J39" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3487,7 +3711,7 @@
       <c r="E40">
         <v>2013</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="11">
         <v>7.9</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -3495,7 +3719,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="13">
         <v>7.9</v>
       </c>
       <c r="I40" t="inlineStr">
@@ -3503,7 +3727,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J40" s="12" t="inlineStr">
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3536,7 +3760,7 @@
       <c r="E41">
         <v>2013</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="11">
         <v>1.3</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -3544,7 +3768,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="13">
         <v>1.3</v>
       </c>
       <c r="I41" t="inlineStr">
@@ -3552,7 +3776,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J41" s="12" t="inlineStr">
+      <c r="J41" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3585,7 +3809,7 @@
       <c r="E42">
         <v>2013</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="11">
         <v>3.2</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -3593,7 +3817,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="13">
         <v>3.1</v>
       </c>
       <c r="I42" t="inlineStr">
@@ -3601,7 +3825,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J42" s="12" t="inlineStr">
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3613,49 +3837,49 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E43" s="3">
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E43" s="10">
         <v>2013</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="12">
         <v>4.84</v>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H43" s="11">
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H43" s="14">
         <v>4.82</v>
       </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J43" s="13" t="e">
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J43" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3683,7 +3907,7 @@
       <c r="E44">
         <v>2014</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="11">
         <v>4.8</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -3691,7 +3915,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="13">
         <v>4.8</v>
       </c>
       <c r="I44" t="inlineStr">
@@ -3699,7 +3923,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3732,7 +3956,7 @@
       <c r="E45">
         <v>2014</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="11">
         <v>6.5</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -3740,7 +3964,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="13">
         <v>6.5</v>
       </c>
       <c r="I45" t="inlineStr">
@@ -3748,7 +3972,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3781,7 +4005,7 @@
       <c r="E46">
         <v>2014</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="11">
         <v>3.1</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -3789,7 +4013,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="13">
         <v>3.1</v>
       </c>
       <c r="I46" t="inlineStr">
@@ -3797,7 +4021,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J46" s="12" t="inlineStr">
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3830,7 +4054,7 @@
       <c r="E47">
         <v>2014</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="11">
         <v>2.8</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -3838,7 +4062,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="13">
         <v>2.8</v>
       </c>
       <c r="I47" t="inlineStr">
@@ -3846,7 +4070,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3879,7 +4103,7 @@
       <c r="E48">
         <v>2014</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="11">
         <v>2.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -3887,7 +4111,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="13">
         <v>2.3</v>
       </c>
       <c r="I48" t="inlineStr">
@@ -3895,7 +4119,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="15">
         <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -3905,49 +4129,49 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E49" s="3">
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E49" s="10">
         <v>2014</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="12">
         <v>3.86</v>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H49" s="11">
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H49" s="14">
         <v>3.9</v>
       </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J49" s="13">
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J49" s="16">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3975,7 +4199,7 @@
       <c r="E50">
         <v>2015</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="11">
         <v>0.3</v>
       </c>
       <c r="G50" t="inlineStr">
@@ -3983,7 +4207,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="13">
         <v>0.3</v>
       </c>
       <c r="I50" t="inlineStr">
@@ -3991,7 +4215,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4024,7 +4248,7 @@
       <c r="E51">
         <v>2015</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="11">
         <v>0.7</v>
       </c>
       <c r="G51" t="inlineStr">
@@ -4032,7 +4256,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="13">
         <v>0.7</v>
       </c>
       <c r="I51" t="inlineStr">
@@ -4040,7 +4264,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J51" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4073,7 +4297,7 @@
       <c r="E52">
         <v>2015</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="11">
         <v>7.7</v>
       </c>
       <c r="G52" t="inlineStr">
@@ -4081,7 +4305,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="13">
         <v>7.7</v>
       </c>
       <c r="I52" t="inlineStr">
@@ -4089,7 +4313,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J52" s="12" t="inlineStr">
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4122,7 +4346,7 @@
       <c r="E53">
         <v>2015</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="11">
         <v>0.7</v>
       </c>
       <c r="G53" t="inlineStr">
@@ -4130,7 +4354,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="13">
         <v>0.7</v>
       </c>
       <c r="I53" t="inlineStr">
@@ -4138,7 +4362,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J53" s="12" t="inlineStr">
+      <c r="J53" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4171,7 +4395,7 @@
       <c r="E54">
         <v>2015</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="11">
         <v>1.4</v>
       </c>
       <c r="G54" t="inlineStr">
@@ -4179,7 +4403,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="13">
         <v>0.7</v>
       </c>
       <c r="I54" t="inlineStr">
@@ -4187,7 +4411,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J54" s="12" t="inlineStr">
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4199,49 +4423,49 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E55" s="3">
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E55" s="10">
         <v>2015</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="12">
         <v>2.16</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H55" s="11">
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H55" s="14">
         <v>2.02</v>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J55" s="13" t="e">
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J55" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4269,7 +4493,7 @@
       <c r="E56">
         <v>2016</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="11">
         <v>0.9</v>
       </c>
       <c r="G56" t="inlineStr">
@@ -4277,7 +4501,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H56" s="13" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4287,7 +4511,7 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J56" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4320,7 +4544,7 @@
       <c r="E57">
         <v>2016</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="11">
         <v>1.4</v>
       </c>
       <c r="G57" t="inlineStr">
@@ -4328,7 +4552,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="13">
         <v>1.4</v>
       </c>
       <c r="I57" t="inlineStr">
@@ -4336,7 +4560,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J57" s="12" t="inlineStr">
+      <c r="J57" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4369,7 +4593,7 @@
       <c r="E58">
         <v>2016</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="11">
         <v>4.7</v>
       </c>
       <c r="G58" t="inlineStr">
@@ -4377,7 +4601,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="13">
         <v>3.5</v>
       </c>
       <c r="I58" t="inlineStr">
@@ -4385,7 +4609,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J58" s="12" t="inlineStr">
+      <c r="J58" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4418,7 +4642,7 @@
       <c r="E59">
         <v>2016</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="11">
         <v>0.1</v>
       </c>
       <c r="G59" t="inlineStr">
@@ -4426,7 +4650,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="13">
         <v>0.1</v>
       </c>
       <c r="I59" t="inlineStr">
@@ -4434,7 +4658,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J59" s="12" t="inlineStr">
+      <c r="J59" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4467,7 +4691,7 @@
       <c r="E60">
         <v>2016</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="11">
         <v>0.9</v>
       </c>
       <c r="G60" t="inlineStr">
@@ -4475,7 +4699,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="13">
         <v>1</v>
       </c>
       <c r="I60" t="inlineStr">
@@ -4483,7 +4707,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J60" s="12" t="inlineStr">
+      <c r="J60" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4495,49 +4719,49 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E61" s="3">
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E61" s="10">
         <v>2016</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="12">
         <v>1.6</v>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H61" s="11">
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H61" s="14">
         <v>1.5</v>
       </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J61" s="13" t="e">
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J61" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="K61" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4565,7 +4789,7 @@
       <c r="E62">
         <v>2017</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="11">
         <v>2.5</v>
       </c>
       <c r="G62" t="inlineStr">
@@ -4573,7 +4797,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="13" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4583,7 +4807,7 @@
           <t>ND</t>
         </is>
       </c>
-      <c r="J62" s="12" t="inlineStr">
+      <c r="J62" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4616,7 +4840,7 @@
       <c r="E63">
         <v>2017</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="11">
         <v>3.4</v>
       </c>
       <c r="G63" t="inlineStr">
@@ -4624,7 +4848,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="13">
         <v>3.4</v>
       </c>
       <c r="I63" t="inlineStr">
@@ -4632,7 +4856,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J63" s="12" t="inlineStr">
+      <c r="J63" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4665,7 +4889,7 @@
       <c r="E64">
         <v>2017</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="11">
         <v>6.9</v>
       </c>
       <c r="G64" t="inlineStr">
@@ -4673,7 +4897,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H64" s="10">
+      <c r="H64" s="13">
         <v>11.8</v>
       </c>
       <c r="I64" t="inlineStr">
@@ -4681,7 +4905,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J64" s="12" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4714,7 +4938,7 @@
       <c r="E65">
         <v>2017</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="11">
         <v>0.1</v>
       </c>
       <c r="G65" t="inlineStr">
@@ -4722,7 +4946,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H65" s="10">
+      <c r="H65" s="13">
         <v>0.1</v>
       </c>
       <c r="I65" t="inlineStr">
@@ -4730,7 +4954,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J65" s="12" t="inlineStr">
+      <c r="J65" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4763,7 +4987,7 @@
       <c r="E66">
         <v>2017</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="11">
         <v>0.7</v>
       </c>
       <c r="G66" t="inlineStr">
@@ -4771,7 +4995,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="13">
         <v>0.4</v>
       </c>
       <c r="I66" t="inlineStr">
@@ -4779,7 +5003,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J66" s="12" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4791,49 +5015,49 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E67" s="3">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E67" s="10">
         <v>2017</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67" s="12">
         <v>2.72</v>
       </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H67" s="11">
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H67" s="14">
         <v>3.925</v>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J67" s="13" t="e">
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J67" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K67" s="3" t="inlineStr">
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4861,7 +5085,7 @@
       <c r="E68">
         <v>2018</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="11">
         <v>1.1</v>
       </c>
       <c r="G68" t="inlineStr">
@@ -4869,7 +5093,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="13">
         <v>1.1</v>
       </c>
       <c r="I68" t="inlineStr">
@@ -4877,7 +5101,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J68" s="12" t="inlineStr">
+      <c r="J68" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4910,7 +5134,7 @@
       <c r="E69">
         <v>2018</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="11">
         <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
@@ -4918,7 +5142,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="13">
         <v>0</v>
       </c>
       <c r="I69" t="inlineStr">
@@ -4926,7 +5150,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J69" s="12" t="inlineStr">
+      <c r="J69" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4959,7 +5183,7 @@
       <c r="E70">
         <v>2018</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="11">
         <v>6.5</v>
       </c>
       <c r="G70" t="inlineStr">
@@ -4967,7 +5191,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="13">
         <v>6.5</v>
       </c>
       <c r="I70" t="inlineStr">
@@ -4975,7 +5199,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J70" s="12" t="inlineStr">
+      <c r="J70" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5008,7 +5232,7 @@
       <c r="E71">
         <v>2018</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="11">
         <v>0.1</v>
       </c>
       <c r="G71" t="inlineStr">
@@ -5016,7 +5240,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H71" s="10">
+      <c r="H71" s="13">
         <v>0.1</v>
       </c>
       <c r="I71" t="inlineStr">
@@ -5024,7 +5248,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J71" s="12" t="inlineStr">
+      <c r="J71" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5057,7 +5281,7 @@
       <c r="E72">
         <v>2018</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="11">
         <v>0.2</v>
       </c>
       <c r="G72" t="inlineStr">
@@ -5065,7 +5289,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="13">
         <v>0.2</v>
       </c>
       <c r="I72" t="inlineStr">
@@ -5073,7 +5297,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J72" s="12" t="inlineStr">
+      <c r="J72" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5085,49 +5309,49 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E73" s="3">
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E73" s="10">
         <v>2018</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="12">
         <v>1.58</v>
       </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H73" s="11">
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H73" s="14">
         <v>1.58</v>
       </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J73" s="13" t="e">
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J73" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K73" s="3" t="inlineStr">
+      <c r="K73" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5155,7 +5379,7 @@
       <c r="E74">
         <v>2019</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="11">
         <v>3.4</v>
       </c>
       <c r="G74" t="inlineStr">
@@ -5163,7 +5387,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="13">
         <v>3.4</v>
       </c>
       <c r="I74" t="inlineStr">
@@ -5171,7 +5395,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J74" s="12" t="inlineStr">
+      <c r="J74" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5204,7 +5428,7 @@
       <c r="E75">
         <v>2019</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="11">
         <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
@@ -5212,7 +5436,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="13">
         <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
@@ -5220,7 +5444,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J75" s="12" t="inlineStr">
+      <c r="J75" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5253,7 +5477,7 @@
       <c r="E76">
         <v>2019</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="11">
         <v>4.2</v>
       </c>
       <c r="G76" t="inlineStr">
@@ -5261,7 +5485,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H76" s="10">
+      <c r="H76" s="13">
         <v>4.2</v>
       </c>
       <c r="I76" t="inlineStr">
@@ -5269,7 +5493,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J76" s="12" t="inlineStr">
+      <c r="J76" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5302,7 +5526,7 @@
       <c r="E77">
         <v>2019</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="11">
         <v>0</v>
       </c>
       <c r="G77" t="inlineStr">
@@ -5310,7 +5534,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H77" s="10">
+      <c r="H77" s="13">
         <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
@@ -5318,7 +5542,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J77" s="12" t="inlineStr">
+      <c r="J77" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5351,7 +5575,7 @@
       <c r="E78">
         <v>2019</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="11">
         <v>0.7</v>
       </c>
       <c r="G78" t="inlineStr">
@@ -5359,7 +5583,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H78" s="10">
+      <c r="H78" s="13">
         <v>0.7</v>
       </c>
       <c r="I78" t="inlineStr">
@@ -5367,7 +5591,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J78" s="12" t="inlineStr">
+      <c r="J78" s="15" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5379,49 +5603,49 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E79" s="3">
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E79" s="10">
         <v>2019</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="12">
         <v>1.66</v>
       </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H79" s="11">
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H79" s="14">
         <v>1.66</v>
       </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J79" s="13" t="e">
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J79" s="16" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K79" s="3" t="inlineStr">
+      <c r="K79" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5449,7 +5673,7 @@
       <c r="E80">
         <v>2020</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="11">
         <v>8.5</v>
       </c>
       <c r="G80" t="inlineStr">
@@ -5457,7 +5681,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="13">
         <v>0.9</v>
       </c>
       <c r="I80" t="inlineStr">
@@ -5465,7 +5689,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J80" s="12">
+      <c r="J80" s="15">
         <v>75</v>
       </c>
       <c r="K80" t="inlineStr">
@@ -5496,7 +5720,7 @@
       <c r="E81">
         <v>2020</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="11">
         <v>6.3</v>
       </c>
       <c r="G81" t="inlineStr">
@@ -5504,7 +5728,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H81" s="10">
+      <c r="H81" s="13">
         <v>0</v>
       </c>
       <c r="I81" t="inlineStr">
@@ -5512,7 +5736,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J81" s="12">
+      <c r="J81" s="15">
         <v>100</v>
       </c>
       <c r="K81" t="inlineStr">
@@ -5543,7 +5767,7 @@
       <c r="E82">
         <v>2020</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="11">
         <v>13.9</v>
       </c>
       <c r="G82" t="inlineStr">
@@ -5551,7 +5775,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H82" s="10">
+      <c r="H82" s="13">
         <v>13.6</v>
       </c>
       <c r="I82" t="inlineStr">
@@ -5559,7 +5783,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J82" s="12">
+      <c r="J82" s="15">
         <v>15.3</v>
       </c>
       <c r="K82" t="inlineStr">
@@ -5590,7 +5814,7 @@
       <c r="E83">
         <v>2020</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="11">
         <v>5.8</v>
       </c>
       <c r="G83" t="inlineStr">
@@ -5598,7 +5822,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H83" s="10">
+      <c r="H83" s="13">
         <v>0.6</v>
       </c>
       <c r="I83" t="inlineStr">
@@ -5606,7 +5830,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J83" s="12">
+      <c r="J83" s="15">
         <v>31.7</v>
       </c>
       <c r="K83" t="inlineStr">
@@ -5637,7 +5861,7 @@
       <c r="E84">
         <v>2020</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="11">
         <v>6.6</v>
       </c>
       <c r="G84" t="inlineStr">
@@ -5645,7 +5869,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H84" s="10">
+      <c r="H84" s="13">
         <v>0</v>
       </c>
       <c r="I84" t="inlineStr">
@@ -5653,7 +5877,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J84" s="12">
+      <c r="J84" s="15">
         <v>22.3</v>
       </c>
       <c r="K84" t="inlineStr">
@@ -5663,49 +5887,49 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E85" s="3">
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E85" s="10">
         <v>2020</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="12">
         <v>8.22</v>
       </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H85" s="11">
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H85" s="14">
         <v>3.02</v>
       </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J85" s="13">
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J85" s="16">
         <v>48.86</v>
       </c>
-      <c r="K85" s="3" t="inlineStr">
+      <c r="K85" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5733,7 +5957,7 @@
       <c r="E86">
         <v>2021</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="11">
         <v>11.9</v>
       </c>
       <c r="G86" t="inlineStr">
@@ -5741,7 +5965,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H86" s="10">
+      <c r="H86" s="13">
         <v>3.4</v>
       </c>
       <c r="I86" t="inlineStr">
@@ -5749,7 +5973,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J86" s="12">
+      <c r="J86" s="15">
         <v>54.1</v>
       </c>
       <c r="K86" t="inlineStr">
@@ -5780,7 +6004,7 @@
       <c r="E87">
         <v>2021</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="11">
         <v>6.5</v>
       </c>
       <c r="G87" t="inlineStr">
@@ -5788,7 +6012,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H87" s="10">
+      <c r="H87" s="13">
         <v>1.2</v>
       </c>
       <c r="I87" t="inlineStr">
@@ -5796,7 +6020,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J87" s="12">
+      <c r="J87" s="15">
         <v>100</v>
       </c>
       <c r="K87" t="inlineStr">
@@ -5827,7 +6051,7 @@
       <c r="E88">
         <v>2021</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="11">
         <v>18.2</v>
       </c>
       <c r="G88" t="inlineStr">
@@ -5835,7 +6059,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="H88" s="10">
+      <c r="H88" s="13">
         <v>19.4</v>
       </c>
       <c r="I88" t="inlineStr">
@@ -5843,7 +6067,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J88" s="12">
+      <c r="J88" s="15">
         <v>14.8</v>
       </c>
       <c r="K88" t="inlineStr">
@@ -5874,7 +6098,7 @@
       <c r="E89">
         <v>2021</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="11">
         <v>10.4</v>
       </c>
       <c r="G89" t="inlineStr">
@@ -5882,7 +6106,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="13">
         <v>0.3</v>
       </c>
       <c r="I89" t="inlineStr">
@@ -5890,7 +6114,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J89" s="12">
+      <c r="J89" s="15">
         <v>25.7</v>
       </c>
       <c r="K89" t="inlineStr">
@@ -5921,7 +6145,7 @@
       <c r="E90">
         <v>2021</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="11">
         <v>5.8</v>
       </c>
       <c r="G90" t="inlineStr">
@@ -5929,7 +6153,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H90" s="10">
+      <c r="H90" s="13">
         <v>0.1</v>
       </c>
       <c r="I90" t="inlineStr">
@@ -5937,7 +6161,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J90" s="12">
+      <c r="J90" s="15">
         <v>23.6</v>
       </c>
       <c r="K90" t="inlineStr">
@@ -5947,49 +6171,49 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E91" s="3">
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E91" s="10">
         <v>2021</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="12">
         <v>10.56</v>
       </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H91" s="11">
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H91" s="14">
         <v>4.88</v>
       </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J91" s="13">
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J91" s="16">
         <v>43.64</v>
       </c>
-      <c r="K91" s="3" t="inlineStr">
+      <c r="K91" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6017,7 +6241,7 @@
       <c r="E92">
         <v>2022</v>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="11">
         <v>4.7</v>
       </c>
       <c r="G92" t="inlineStr">
@@ -6025,7 +6249,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H92" s="10">
+      <c r="H92" s="13">
         <v>0.4</v>
       </c>
       <c r="I92" t="inlineStr">
@@ -6033,7 +6257,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J92" s="12">
+      <c r="J92" s="15">
         <v>24</v>
       </c>
       <c r="K92" t="inlineStr">
@@ -6064,7 +6288,7 @@
       <c r="E93">
         <v>2022</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="11">
         <v>5.9</v>
       </c>
       <c r="G93" t="inlineStr">
@@ -6072,7 +6296,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="13">
         <v>0.7</v>
       </c>
       <c r="I93" t="inlineStr">
@@ -6080,7 +6304,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J93" s="12">
+      <c r="J93" s="15">
         <v>100</v>
       </c>
       <c r="K93" t="inlineStr">
@@ -6111,7 +6335,7 @@
       <c r="E94">
         <v>2022</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="11">
         <v>9.2</v>
       </c>
       <c r="G94" t="inlineStr">
@@ -6119,7 +6343,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="13">
         <v>8.5</v>
       </c>
       <c r="I94" t="inlineStr">
@@ -6127,7 +6351,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="J94" s="12">
+      <c r="J94" s="15">
         <v>11.3</v>
       </c>
       <c r="K94" t="inlineStr">
@@ -6158,7 +6382,7 @@
       <c r="E95">
         <v>2022</v>
       </c>
-      <c r="F95" s="8">
+      <c r="F95" s="11">
         <v>11.3</v>
       </c>
       <c r="G95" t="inlineStr">
@@ -6166,7 +6390,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="13">
         <v>0.8</v>
       </c>
       <c r="I95" t="inlineStr">
@@ -6174,7 +6398,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J95" s="12">
+      <c r="J95" s="15">
         <v>31.8</v>
       </c>
       <c r="K95" t="inlineStr">
@@ -6205,7 +6429,7 @@
       <c r="E96">
         <v>2022</v>
       </c>
-      <c r="F96" s="8">
+      <c r="F96" s="11">
         <v>0.7</v>
       </c>
       <c r="G96" t="inlineStr">
@@ -6213,7 +6437,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H96" s="10">
+      <c r="H96" s="13">
         <v>0.9</v>
       </c>
       <c r="I96" t="inlineStr">
@@ -6221,7 +6445,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J96" s="12">
+      <c r="J96" s="15">
         <v>0</v>
       </c>
       <c r="K96" t="inlineStr">
@@ -6231,49 +6455,49 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E97" s="3">
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E97" s="10">
         <v>2022</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="12">
         <v>6.36</v>
       </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H97" s="11">
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H97" s="14">
         <v>2.26</v>
       </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J97" s="13">
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J97" s="16">
         <v>33.42</v>
       </c>
-      <c r="K97" s="3" t="inlineStr">
+      <c r="K97" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6301,7 +6525,7 @@
       <c r="E98">
         <v>2023</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="11">
         <v>7.1</v>
       </c>
       <c r="G98" t="inlineStr">
@@ -6309,7 +6533,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="13">
         <v>0.3</v>
       </c>
       <c r="I98" t="inlineStr">
@@ -6317,7 +6541,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J98" s="12">
+      <c r="J98" s="15">
         <v>33.3</v>
       </c>
       <c r="K98" t="inlineStr">
@@ -6348,7 +6572,7 @@
       <c r="E99">
         <v>2023</v>
       </c>
-      <c r="F99" s="8">
+      <c r="F99" s="11">
         <v>6.5</v>
       </c>
       <c r="G99" t="inlineStr">
@@ -6356,7 +6580,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H99" s="10">
+      <c r="H99" s="13">
         <v>1.3</v>
       </c>
       <c r="I99" t="inlineStr">
@@ -6364,7 +6588,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J99" s="12">
+      <c r="J99" s="15">
         <v>98.2</v>
       </c>
       <c r="K99" t="inlineStr">
@@ -6395,7 +6619,7 @@
       <c r="E100">
         <v>2023</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F100" s="11">
         <v>6.2</v>
       </c>
       <c r="G100" t="inlineStr">
@@ -6403,7 +6627,7 @@
           <t>Riesgo bajo</t>
         </is>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="13">
         <v>1.2</v>
       </c>
       <c r="I100" t="inlineStr">
@@ -6411,7 +6635,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J100" s="12">
+      <c r="J100" s="15">
         <v>21.9</v>
       </c>
       <c r="K100" t="inlineStr">
@@ -6442,7 +6666,7 @@
       <c r="E101">
         <v>2023</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="11">
         <v>2.8</v>
       </c>
       <c r="G101" t="inlineStr">
@@ -6450,7 +6674,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="13">
         <v>0.7</v>
       </c>
       <c r="I101" t="inlineStr">
@@ -6458,7 +6682,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J101" s="12">
+      <c r="J101" s="15">
         <v>12</v>
       </c>
       <c r="K101" t="inlineStr">
@@ -6489,7 +6713,7 @@
       <c r="E102">
         <v>2023</v>
       </c>
-      <c r="F102" s="8">
+      <c r="F102" s="11">
         <v>3.2</v>
       </c>
       <c r="G102" t="inlineStr">
@@ -6497,7 +6721,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="13">
         <v>0</v>
       </c>
       <c r="I102" t="inlineStr">
@@ -6505,7 +6729,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J102" s="12">
+      <c r="J102" s="15">
         <v>12.6</v>
       </c>
       <c r="K102" t="inlineStr">
@@ -6515,49 +6739,49 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E103" s="3">
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E103" s="10">
         <v>2023</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="12">
         <v>5.16</v>
       </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H103" s="11">
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H103" s="14">
         <v>0.7</v>
       </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J103" s="13">
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J103" s="16">
         <v>35.6</v>
       </c>
-      <c r="K103" s="3" t="inlineStr">
+      <c r="K103" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6585,7 +6809,7 @@
       <c r="E104">
         <v>2024</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="11">
         <v>5.2</v>
       </c>
       <c r="G104" t="inlineStr">
@@ -6593,7 +6817,7 @@
           <t>Bajo riesgo</t>
         </is>
       </c>
-      <c r="H104" s="10">
+      <c r="H104" s="13">
         <v>0.8</v>
       </c>
       <c r="I104" t="inlineStr">
@@ -6601,7 +6825,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J104" s="12">
+      <c r="J104" s="15">
         <v>38.5</v>
       </c>
       <c r="K104" t="inlineStr">
@@ -6632,7 +6856,7 @@
       <c r="E105">
         <v>2024</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="11">
         <v>5.4</v>
       </c>
       <c r="G105" t="inlineStr">
@@ -6640,7 +6864,7 @@
           <t>Bajo riesgo</t>
         </is>
       </c>
-      <c r="H105" s="10">
+      <c r="H105" s="13">
         <v>0.6</v>
       </c>
       <c r="I105" t="inlineStr">
@@ -6648,7 +6872,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J105" s="12">
+      <c r="J105" s="15">
         <v>97.4</v>
       </c>
       <c r="K105" t="inlineStr">
@@ -6679,7 +6903,7 @@
       <c r="E106">
         <v>2024</v>
       </c>
-      <c r="F106" s="8">
+      <c r="F106" s="11">
         <v>13.9</v>
       </c>
       <c r="G106" t="inlineStr">
@@ -6687,7 +6911,7 @@
           <t>Bajo riesgo</t>
         </is>
       </c>
-      <c r="H106" s="10">
+      <c r="H106" s="13">
         <v>14.4</v>
       </c>
       <c r="I106" t="inlineStr">
@@ -6695,7 +6919,7 @@
           <t>Riesgo medio</t>
         </is>
       </c>
-      <c r="J106" s="12">
+      <c r="J106" s="15">
         <v>11.4</v>
       </c>
       <c r="K106" t="inlineStr">
@@ -6726,7 +6950,7 @@
       <c r="E107">
         <v>2024</v>
       </c>
-      <c r="F107" s="8">
+      <c r="F107" s="11">
         <v>1.7</v>
       </c>
       <c r="G107" t="inlineStr">
@@ -6734,7 +6958,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H107" s="10">
+      <c r="H107" s="13">
         <v>0.1</v>
       </c>
       <c r="I107" t="inlineStr">
@@ -6742,7 +6966,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J107" s="12">
+      <c r="J107" s="15">
         <v>5.6</v>
       </c>
       <c r="K107" t="inlineStr">
@@ -6773,7 +6997,7 @@
       <c r="E108">
         <v>2024</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="11">
         <v>0.7</v>
       </c>
       <c r="G108" t="inlineStr">
@@ -6781,7 +7005,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="13">
         <v>1</v>
       </c>
       <c r="I108" t="inlineStr">
@@ -6789,7 +7013,7 @@
           <t>Sin riesgo</t>
         </is>
       </c>
-      <c r="J108" s="12">
+      <c r="J108" s="15">
         <v>0</v>
       </c>
       <c r="K108" t="inlineStr">
@@ -6799,49 +7023,49 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E109" s="3">
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E109" s="10">
         <v>2024</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="12">
         <v>5.38</v>
       </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H109" s="11">
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H109" s="14">
         <v>3.38</v>
       </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J109" s="13">
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J109" s="16">
         <v>30.58</v>
       </c>
-      <c r="K109" s="3" t="inlineStr">
+      <c r="K109" s="10" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -6859,41 +7083,41 @@
   <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Tipo de evento</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Número de eventos</t>
         </is>
@@ -6923,37 +7147,37 @@
           <t>ACCIDENTE TRANSPORTE AEREO</t>
         </is>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>ACCIDENTE TRANSPORTE AEREO</t>
         </is>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="21">
         <v>1</v>
       </c>
     </row>
@@ -6981,37 +7205,37 @@
           <t>ACCIDENTE TRANSPORTE TERRESTRE</t>
         </is>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>ACCIDENTE TRANSPORTE TERRESTRE</t>
         </is>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="21">
         <v>2</v>
       </c>
     </row>
@@ -7039,37 +7263,37 @@
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>AVENIDA TORRENCIAL</t>
         </is>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="21">
         <v>3</v>
       </c>
     </row>
@@ -7097,37 +7321,37 @@
           <t>CRECIENTE SUBITA</t>
         </is>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>CRECIENTE SUBITA</t>
         </is>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="21">
         <v>2</v>
       </c>
     </row>
@@ -7155,37 +7379,37 @@
           <t>GRANIZADA</t>
         </is>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>GRANIZADA</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="21">
         <v>1</v>
       </c>
     </row>
@@ -7213,37 +7437,37 @@
           <t>HELADA</t>
         </is>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>HELADA</t>
         </is>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="21">
         <v>1</v>
       </c>
     </row>
@@ -7271,7 +7495,7 @@
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="20">
         <v>1</v>
       </c>
     </row>
@@ -7299,7 +7523,7 @@
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="20">
         <v>1</v>
       </c>
     </row>
@@ -7327,37 +7551,37 @@
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>INCENDIO DE COBERTURA VEGETAL</t>
         </is>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="21">
         <v>3</v>
       </c>
     </row>
@@ -7385,37 +7609,37 @@
           <t>INCENDIO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>INCENDIO ESTRUCTURAL</t>
         </is>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="21">
         <v>1</v>
       </c>
     </row>
@@ -7443,7 +7667,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="20">
         <v>4</v>
       </c>
     </row>
@@ -7471,7 +7695,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="20">
         <v>2</v>
       </c>
     </row>
@@ -7499,7 +7723,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="20">
         <v>4</v>
       </c>
     </row>
@@ -7527,7 +7751,7 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="20">
         <v>5</v>
       </c>
     </row>
@@ -7555,37 +7779,37 @@
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="20">
         <v>17</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>INCENDIO FORESTAL</t>
         </is>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="21">
         <v>32</v>
       </c>
     </row>
@@ -7613,7 +7837,7 @@
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="20">
         <v>3</v>
       </c>
     </row>
@@ -7641,37 +7865,37 @@
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>INUNDACION</t>
         </is>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="21">
         <v>4</v>
       </c>
     </row>
@@ -7699,7 +7923,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="20">
         <v>5</v>
       </c>
     </row>
@@ -7727,7 +7951,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="20">
         <v>1</v>
       </c>
     </row>
@@ -7755,7 +7979,7 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="20">
         <v>1</v>
       </c>
     </row>
@@ -7783,37 +8007,37 @@
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>MOVIMIENTO EN MASA</t>
         </is>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="21">
         <v>10</v>
       </c>
     </row>
@@ -7841,37 +8065,37 @@
           <t>SISMO</t>
         </is>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>SISMO</t>
         </is>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="21">
         <v>1</v>
       </c>
     </row>
@@ -7899,37 +8123,37 @@
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>TEMPORAL</t>
         </is>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="21">
         <v>1</v>
       </c>
     </row>
@@ -7957,7 +8181,7 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="20">
         <v>3</v>
       </c>
     </row>
@@ -7985,37 +8209,37 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="21">
         <v>6</v>
       </c>
     </row>
@@ -8031,41 +8255,41 @@
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Número de eventos</t>
         </is>
@@ -8093,7 +8317,7 @@
       <c r="E2">
         <v>2019</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="25">
         <v>1</v>
       </c>
     </row>
@@ -8119,35 +8343,35 @@
       <c r="E3">
         <v>2019</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="25">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E4" s="24">
         <v>2019</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="26">
         <v>3</v>
       </c>
     </row>
@@ -8173,7 +8397,7 @@
       <c r="E5">
         <v>2020</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="25">
         <v>3</v>
       </c>
     </row>
@@ -8199,7 +8423,7 @@
       <c r="E6">
         <v>2020</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="25">
         <v>1</v>
       </c>
     </row>
@@ -8225,7 +8449,7 @@
       <c r="E7">
         <v>2020</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="25">
         <v>3</v>
       </c>
     </row>
@@ -8251,35 +8475,35 @@
       <c r="E8">
         <v>2020</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="25">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="3">
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="24">
         <v>2020</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="26">
         <v>10</v>
       </c>
     </row>
@@ -8305,7 +8529,7 @@
       <c r="E10">
         <v>2021</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="25">
         <v>1</v>
       </c>
     </row>
@@ -8331,35 +8555,35 @@
       <c r="E11">
         <v>2021</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="25">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E12" s="3">
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="24">
         <v>2021</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="26">
         <v>6</v>
       </c>
     </row>
@@ -8385,7 +8609,7 @@
       <c r="E13">
         <v>2022</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="25">
         <v>3</v>
       </c>
     </row>
@@ -8411,35 +8635,35 @@
       <c r="E14">
         <v>2022</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="25">
         <v>9</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="3">
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="24">
         <v>2022</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="26">
         <v>12</v>
       </c>
     </row>
@@ -8465,7 +8689,7 @@
       <c r="E16">
         <v>2023</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="25">
         <v>2</v>
       </c>
     </row>
@@ -8491,35 +8715,35 @@
       <c r="E17">
         <v>2023</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E18" s="3">
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" s="24">
         <v>2023</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="26">
         <v>3</v>
       </c>
     </row>
@@ -8545,7 +8769,7 @@
       <c r="E19">
         <v>2024</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="25">
         <v>4</v>
       </c>
     </row>
@@ -8571,7 +8795,7 @@
       <c r="E20">
         <v>2024</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="25">
         <v>1</v>
       </c>
     </row>
@@ -8597,7 +8821,7 @@
       <c r="E21">
         <v>2024</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="25">
         <v>4</v>
       </c>
     </row>
@@ -8623,7 +8847,7 @@
       <c r="E22">
         <v>2024</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="25">
         <v>5</v>
       </c>
     </row>
@@ -8649,35 +8873,35 @@
       <c r="E23">
         <v>2024</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="25">
         <v>20</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E24" s="3">
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="24">
         <v>2024</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="26">
         <v>34</v>
       </c>
     </row>
@@ -8693,64 +8917,64 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="28" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="28" t="inlineStr">
         <is>
           <t>Avenida torrencial</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="28" t="inlineStr">
         <is>
           <t>Movimiento en masa</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>Incendio de cobertura vegetal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="28" t="inlineStr">
         <is>
           <t>Inundación</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="28" t="inlineStr">
         <is>
           <t>Sequía</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="28" t="inlineStr">
         <is>
           <t>Sismo</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="28" t="inlineStr">
         <is>
           <t>Emergencia más prevalente</t>
         </is>
@@ -8770,22 +8994,22 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="30">
         <v>3</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="32">
         <v>0</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <v>0</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="36">
         <v>0</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="38">
         <v>0</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="40">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -8808,22 +9032,22 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="30">
         <v>0</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="32">
         <v>5</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <v>1</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="36">
         <v>3</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="38">
         <v>0</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="40">
         <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -8846,22 +9070,22 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="30">
         <v>0</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="32">
         <v>1</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <v>0</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="36">
         <v>0</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="38">
         <v>0</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="40">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -8884,22 +9108,22 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="32">
         <v>1</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="34">
         <v>1</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="36">
         <v>0</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="38">
         <v>0</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -8922,22 +9146,22 @@
           <t>NORTE</t>
         </is>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="30">
         <v>0</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="32">
         <v>3</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="34">
         <v>1</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="36">
         <v>1</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="38">
         <v>0</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="40">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -8947,80 +9171,80 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="19">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="31">
         <v>3</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <v>10</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="35">
         <v>3</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="37">
         <v>4</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="39">
         <v>0</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="41">
         <v>1</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="29" t="inlineStr">
         <is>
           <t>Movimiento en masa</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>TOTAL SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="19">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="31">
         <v>14</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <v>113</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="35">
         <v>16</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="37">
         <v>10</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="39">
         <v>0</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="41">
         <v>1</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J8" s="29" t="inlineStr">
         <is>
           <t>Movimiento en masa</t>
         </is>
@@ -9038,41 +9262,41 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t>IMRC Exceso de lluvias</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="43" t="inlineStr">
         <is>
           <t>IMRC Déficit de lluvias</t>
         </is>
@@ -9097,10 +9321,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="45">
         <v>44.2692159190449</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="47">
         <v>26.5512781246309</v>
       </c>
     </row>
@@ -9123,10 +9347,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="45">
         <v>38.8862307006087</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="47">
         <v>23.6232204097407</v>
       </c>
     </row>
@@ -9149,10 +9373,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="45">
         <v>37.1384951151091</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="47">
         <v>31.1885302542954</v>
       </c>
     </row>
@@ -9175,10 +9399,10 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="45">
         <v>35.9236001252112</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="47">
         <v>26.5119536669525</v>
       </c>
     </row>
@@ -9201,66 +9425,66 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="45">
         <v>41.217172849319</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="47">
         <v>27.0897919339764</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>PROVINCIA DEL RIO GRANDE</t>
-        </is>
-      </c>
-      <c r="E7" s="31">
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>PROVINCIA DEL RIO GRANDE</t>
+        </is>
+      </c>
+      <c r="E7" s="46">
         <v>39.4869429418585</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="48">
         <v>26.9929548779192</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ANTIOQUIA</t>
         </is>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="46">
         <v>46.9223181824352</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="48">
         <v>26.5093698141241</v>
       </c>
     </row>
@@ -9276,35 +9500,35 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Pérdida de cobertura arbórea 2001-2023 (%)</t>
         </is>
@@ -9329,7 +9553,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="52">
         <v>0.019</v>
       </c>
     </row>
@@ -9352,7 +9576,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="52">
         <v>0.064</v>
       </c>
     </row>
@@ -9375,7 +9599,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="52">
         <v>0.069</v>
       </c>
     </row>
@@ -9398,7 +9622,7 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="52">
         <v>0.061</v>
       </c>
     </row>
@@ -9421,82 +9645,82 @@
           <t>PROVINCIA DEL RIO GRANDE</t>
         </is>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="52">
         <v>0.09</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA DEL RÍO GRANDE</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E7" s="35">
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E7" s="53">
         <v>0.0606</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE SUBREGIÓN NORTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E8" s="35">
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E8" s="53">
         <v>0.0700588235294118</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="35">
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E9" s="53">
         <v>0.09304</v>
       </c>
     </row>
@@ -9512,23 +9736,23 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="55" t="inlineStr">
         <is>
           <t>area_km2</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="55" t="inlineStr">
         <is>
           <t>participacion</t>
         </is>
@@ -9598,29 +9822,29 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="57" t="inlineStr">
         <is>
           <t>irca</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="57" t="inlineStr">
         <is>
           <t>irca_urbano</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="57" t="inlineStr">
         <is>
           <t>irca_rural</t>
         </is>
